--- a/chapters/10/guides/AIHE-RG04/edit/xlsx/AIHE-RG04_register.xlsx
+++ b/chapters/10/guides/AIHE-RG04/edit/xlsx/AIHE-RG04_register.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R8afbe8c0ec8c4cdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Register" sheetId="2" r:id="Rdfd9d13c24074431"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local Copy" sheetId="3" r:id="R605ce5a38f894f2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R416994f62f794fdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Register" sheetId="2" r:id="Rff92d2243cf4424b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local Copy" sheetId="3" r:id="R05c6391fa44649bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -189,14 +189,10 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyAlignment="1">
@@ -321,9 +317,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -682,10 +676,8 @@
           <x:t xml:space="preserve">Additional alignment</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2, 5, 7, 9, 10, 12-15</x:t>
-        </x:is>
+      <x:c r="B5" s="27" t="str">
+        <x:v>2, 5, 7, 9, 10, 12</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
